--- a/dataset/01.w_Defects/st_cross_thread_access.xlsx
+++ b/dataset/01.w_Defects/st_cross_thread_access.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pthread_mutex_t st_cross_thread_access_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_001_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_001_glb_data = 0; int *st_cross_thread_access_001_glb_ptr; pthread_mutex_t st_cross_thread_access_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_002_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; unsigned long st_cross_thread_access_002_glb_data = 0; int const st_cross_thread_access_002_var = 10; int arr1[5]={1,2,3,4,5}; int * st_cross_thread_access_002_glb_ptr = arr1; pthread_mutex_t st_cross_thread_access_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_003_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; float st_cross_thread_access_003_glb_data = 1000.0; float st_cross_thread_access_003_glb_data1 = 10.0; float *st_cross_thread_access_003_glb_ptr = &amp;st_cross_thread_access_003_glb_data1; pthread_mutex_t st_cross_thread_access_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char *buf1="String1"; char *buf2="String2"; char **pbuf[2] = {&amp;buf1, &amp;buf2}; pthread_mutex_t st_cross_thread_access_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_005_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_005_glb_data = 0; int st_cross_thread_access_005_thread_set = NO_THREAD; pthread_mutex_t st_cross_thread_access_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; st_cross_thread_access_006_s_001 s1 ={10,20}; st_cross_thread_access_006_s_001 *sptr = &amp;s1; extern volatile int vflag; void st_cross_thread_access_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, st_cross_thread_access_004_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, st_cross_thread_access_004_tsk_002, (void *)t2); /*pthread_join(th1, NULL); pthread_join(th2, NULL);*/ #endif /* defined(CHECKER_POLYSPACE) */ } void * st_cross_thread_access_004_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;st_cross_thread_access_004_glb_mutex_2 ); strcpy(*pbuf[0],"TEST");/*Tool should detect this line as error*/ /*ERROR:Cross thread stack access error*/ pthread_mutex_unlock( &amp;st_cross_thread_access_004_glb_mutex_2 ); } i--; } #if defined PRINT_DEBUG printf("Task4_2! Cross thread stack access, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *st_cross_thread_access_004_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; char *buf11="String111"; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;st_cross_thread_access_004_glb_mutex_1 ); pbuf[0] = &amp;buf11; pthread_mutex_unlock( &amp;st_cross_thread_access_004_glb_mutex_1 ); } i--; } #if defined PRINT_DEBUG printf("Task4_1! Cross thread stack access, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t st_cross_thread_access_001_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_001_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_001_glb_data = 0; int *st_cross_thread_access_001_glb_ptr; pthread_mutex_t st_cross_thread_access_002_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_002_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; unsigned long st_cross_thread_access_002_glb_data = 0; int const st_cross_thread_access_002_var = 10; int arr1[5]={1,2,3,4,5}; int * st_cross_thread_access_002_glb_ptr = arr1; pthread_mutex_t st_cross_thread_access_003_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_003_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; float st_cross_thread_access_003_glb_data = 1000.0; float st_cross_thread_access_003_glb_data1 = 10.0; float *st_cross_thread_access_003_glb_ptr = &amp;st_cross_thread_access_003_glb_data1; pthread_mutex_t st_cross_thread_access_004_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_004_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; char *buf1="String1"; char *buf2="String2"; char **pbuf[2] = {&amp;buf1, &amp;buf2}; pthread_mutex_t st_cross_thread_access_005_glb_mutex = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_005_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; int st_cross_thread_access_005_glb_data = 0; int st_cross_thread_access_005_thread_set = NO_THREAD; pthread_mutex_t st_cross_thread_access_006_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t st_cross_thread_access_006_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; st_cross_thread_access_006_s_001 s1 ={10,20}; st_cross_thread_access_006_s_001 *sptr = &amp;s1; extern volatile int vflag; void st_cross_thread_access_004 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, st_cross_thread_access_004_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, st_cross_thread_access_004_tsk_002, (void *)t2); /*pthread_join(th1, NULL); pthread_join(th2, NULL);*/ #endif /* defined(CHECKER_POLYSPACE) */ } void *st_cross_thread_access_004_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i = 5; ip = (long)input; ip = ip *10; char *buf11="String111"; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;st_cross_thread_access_004_glb_mutex_1 ); pbuf[0] = &amp;buf11; pthread_mutex_unlock( &amp;st_cross_thread_access_004_glb_mutex_1 ); } i--; } #if defined PRINT_DEBUG printf("Task4_1! Cross thread stack access, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * st_cross_thread_access_004_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; int i=5; ip = (long)input; ip = ip *20; while (i&gt;0) { if (ip &gt;= 0) { pthread_mutex_lock( &amp;st_cross_thread_access_004_glb_mutex_2 ); strcpy(*pbuf[0],"TEST");/*Tool should detect this line as error*/ /*ERROR:Cross thread stack access error*/ pthread_mutex_unlock( &amp;st_cross_thread_access_004_glb_mutex_2 ); } i--; } #if defined PRINT_DEBUG printf("Task4_2! Cross thread stack access, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
